--- a/data/Can Transitions 9_25.xlsx
+++ b/data/Can Transitions 9_25.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/balapradeepkonda_alamancefoods_com/Documents/Documents/GitHub/Bala_Can_SupplyChain/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{6789C9C6-A055-4C3F-A8E8-1767869AC47B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47BA4D2B-42D5-4F3F-9472-E9927B039438}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{B4A1369C-FDA8-4210-B800-9E801E204FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23FA03F5-5009-47B4-8C02-C129FC360F87}"/>
   <bookViews>
     <workbookView xWindow="11244" yWindow="-17472" windowWidth="30936" windowHeight="16776" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="90">
   <si>
     <t>ITEM DESCRIPTION</t>
   </si>
@@ -288,6 +288,30 @@
   </si>
   <si>
     <t>AS7</t>
+  </si>
+  <si>
+    <t>A05-G</t>
+  </si>
+  <si>
+    <t>A05-G2</t>
+  </si>
+  <si>
+    <t>A13</t>
+  </si>
+  <si>
+    <t>A13-A</t>
+  </si>
+  <si>
+    <t>Classic Cream Gold Label 12pk/15oz 19.5% CLEAN</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Classic Cream 12pk/15oz 18.0% REG</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -317,7 +341,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -352,6 +376,18 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -430,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -464,6 +500,20 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -817,17 +867,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -855,10 +905,10 @@
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="15"/>
+      <c r="J1" s="21"/>
     </row>
     <row r="2" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -885,10 +935,10 @@
       <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="13"/>
+      <c r="J2" s="19"/>
     </row>
     <row r="3" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -915,10 +965,10 @@
       <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="13"/>
+      <c r="J3" s="19"/>
     </row>
     <row r="4" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
@@ -943,10 +993,10 @@
       <c r="H4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" s="13"/>
+      <c r="I4" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="19"/>
     </row>
     <row r="5" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
@@ -971,10 +1021,10 @@
       <c r="H5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J5" s="13"/>
+      <c r="I5" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="19"/>
     </row>
     <row r="6" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
@@ -999,10 +1049,10 @@
       <c r="H6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="13"/>
+      <c r="I6" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" s="19"/>
     </row>
     <row r="7" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
@@ -1027,10 +1077,10 @@
       <c r="H7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="13"/>
+      <c r="I7" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J7" s="19"/>
     </row>
     <row r="8" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
@@ -1055,10 +1105,10 @@
       <c r="H8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J8" s="13"/>
+      <c r="J8" s="19"/>
     </row>
     <row r="9" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
@@ -1083,10 +1133,10 @@
       <c r="H9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="13"/>
+      <c r="I9" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="19"/>
     </row>
     <row r="10" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
@@ -1111,10 +1161,10 @@
       <c r="H10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J10" s="13"/>
+      <c r="I10" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="19"/>
     </row>
     <row r="11" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
@@ -1139,10 +1189,10 @@
       <c r="H11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J11" s="13"/>
+      <c r="I11" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="19"/>
     </row>
     <row r="12" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
@@ -1167,10 +1217,10 @@
       <c r="H12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J12" s="13"/>
+      <c r="I12" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="19"/>
     </row>
     <row r="13" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -1195,10 +1245,10 @@
       <c r="H13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J13" s="13"/>
+      <c r="I13" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="19"/>
     </row>
     <row r="14" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
@@ -1223,10 +1273,10 @@
       <c r="H14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" s="13"/>
+      <c r="I14" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" s="19"/>
     </row>
     <row r="15" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
@@ -1251,10 +1301,10 @@
       <c r="H15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J15" s="13"/>
+      <c r="I15" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="19"/>
     </row>
     <row r="16" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
@@ -1279,10 +1329,10 @@
       <c r="H16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I16" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J16" s="13"/>
+      <c r="I16" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="19"/>
     </row>
     <row r="17" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
@@ -1307,10 +1357,10 @@
       <c r="H17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J17" s="13"/>
+      <c r="J17" s="19"/>
     </row>
     <row r="18" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
@@ -1335,10 +1385,10 @@
       <c r="H18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I18" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J18" s="13"/>
+      <c r="I18" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="19"/>
     </row>
     <row r="19" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
@@ -1363,10 +1413,10 @@
       <c r="H19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="I19" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J19" s="13"/>
+      <c r="J19" s="19"/>
     </row>
     <row r="20" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
@@ -1391,10 +1441,10 @@
       <c r="H20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="I20" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J20" s="13"/>
+      <c r="J20" s="19"/>
     </row>
     <row r="21" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
@@ -1419,10 +1469,10 @@
       <c r="H21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J21" s="13"/>
+      <c r="J21" s="19"/>
     </row>
     <row r="22" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
@@ -1447,10 +1497,10 @@
       <c r="H22" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J22" s="13"/>
+      <c r="J22" s="19"/>
     </row>
     <row r="23" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
@@ -1477,10 +1527,10 @@
       <c r="H23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J23" s="13"/>
+      <c r="I23" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J23" s="19"/>
     </row>
     <row r="24" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
@@ -1505,10 +1555,10 @@
       <c r="H24" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J24" s="13"/>
+      <c r="I24" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J24" s="19"/>
     </row>
     <row r="25" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
@@ -1529,10 +1579,10 @@
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J25" s="13"/>
+      <c r="I25" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="19"/>
     </row>
     <row r="26" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
@@ -1557,10 +1607,10 @@
       <c r="H26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J26" s="13"/>
+      <c r="I26" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" s="19"/>
     </row>
     <row r="27" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
@@ -1585,10 +1635,10 @@
       <c r="H27" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="I27" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="13"/>
+      <c r="J27" s="19"/>
     </row>
     <row r="28" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
@@ -1613,10 +1663,10 @@
       <c r="H28" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="I28" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J28" s="13"/>
+      <c r="J28" s="19"/>
     </row>
     <row r="29" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
@@ -1635,16 +1685,16 @@
       <c r="F29" s="7">
         <v>12869</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J29" s="13"/>
+      <c r="G29" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I29" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="J29" s="19"/>
     </row>
     <row r="30" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
@@ -1669,10 +1719,10 @@
       <c r="H30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="I30" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J30" s="13"/>
+      <c r="J30" s="19"/>
     </row>
     <row r="31" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
@@ -1697,10 +1747,10 @@
       <c r="H31" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="I31" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="13"/>
+      <c r="J31" s="19"/>
     </row>
     <row r="32" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
@@ -1725,10 +1775,10 @@
       <c r="H32" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I32" s="12" t="s">
+      <c r="I32" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="J32" s="13"/>
+      <c r="J32" s="19"/>
     </row>
     <row r="33" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
@@ -1753,26 +1803,154 @@
       <c r="H33" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I33" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="J33" s="17"/>
+      <c r="I33" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" s="23"/>
+    </row>
+    <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="7">
+        <v>12246</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="7">
+        <v>12904</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J34" s="17"/>
+    </row>
+    <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="7">
+        <v>12246</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="7">
+        <v>12904</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" s="17"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="7">
+        <v>12007</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="7">
+        <v>12905</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J36" s="17"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D37" s="7">
+        <v>12007</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="7">
+        <v>12905</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J37" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J33" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
+  <autoFilter ref="A1:J37" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
     <filterColumn colId="8" showButton="0"/>
   </autoFilter>
-  <mergeCells count="33">
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
+  <mergeCells count="37">
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I16:J16"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="I23:J23"/>
@@ -1780,22 +1958,10 @@
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="I26:J26"/>
     <mergeCell ref="I27:J27"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/data/Can Transitions 9_25.xlsx
+++ b/data/Can Transitions 9_25.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/balapradeepkonda_alamancefoods_com/Documents/Documents/GitHub/Bala_Can_SupplyChain/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{B4A1369C-FDA8-4210-B800-9E801E204FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23FA03F5-5009-47B4-8C02-C129FC360F87}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{B4A1369C-FDA8-4210-B800-9E801E204FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFBA1C11-1526-4839-B765-5E31B3801E0F}"/>
   <bookViews>
-    <workbookView xWindow="11244" yWindow="-17472" windowWidth="30936" windowHeight="16776" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="86">
   <si>
     <t>ITEM DESCRIPTION</t>
   </si>
@@ -296,22 +296,10 @@
     <t>A05-G2</t>
   </si>
   <si>
-    <t>A13</t>
-  </si>
-  <si>
-    <t>A13-A</t>
-  </si>
-  <si>
     <t>Classic Cream Gold Label 12pk/15oz 19.5% CLEAN</t>
   </si>
   <si>
     <t>Yes</t>
-  </si>
-  <si>
-    <t>Classic Cream 12pk/15oz 18.0% REG</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
 </sst>
 </file>
@@ -341,7 +329,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,12 +369,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -466,7 +448,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -508,7 +490,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -521,17 +502,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -867,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -905,10 +886,10 @@
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="21"/>
+      <c r="J1" s="22"/>
     </row>
     <row r="2" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -935,10 +916,10 @@
       <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="19"/>
+      <c r="J2" s="18"/>
     </row>
     <row r="3" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -965,10 +946,10 @@
       <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="19"/>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
@@ -993,10 +974,10 @@
       <c r="H4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" s="19"/>
+      <c r="I4" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
@@ -1021,10 +1002,10 @@
       <c r="H5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J5" s="19"/>
+      <c r="I5" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="18"/>
     </row>
     <row r="6" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
@@ -1049,10 +1030,10 @@
       <c r="H6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="19"/>
+      <c r="I6" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" s="18"/>
     </row>
     <row r="7" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
@@ -1077,10 +1058,10 @@
       <c r="H7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="19"/>
+      <c r="I7" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
@@ -1105,10 +1086,10 @@
       <c r="H8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J8" s="19"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
@@ -1133,10 +1114,10 @@
       <c r="H9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="19"/>
+      <c r="I9" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
@@ -1161,10 +1142,10 @@
       <c r="H10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J10" s="19"/>
+      <c r="I10" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
@@ -1189,10 +1170,10 @@
       <c r="H11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J11" s="19"/>
+      <c r="I11" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
@@ -1217,10 +1198,10 @@
       <c r="H12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J12" s="19"/>
+      <c r="I12" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="18"/>
     </row>
     <row r="13" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -1245,10 +1226,10 @@
       <c r="H13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J13" s="19"/>
+      <c r="I13" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="18"/>
     </row>
     <row r="14" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
@@ -1273,10 +1254,10 @@
       <c r="H14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" s="19"/>
+      <c r="I14" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" s="18"/>
     </row>
     <row r="15" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
@@ -1301,10 +1282,10 @@
       <c r="H15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J15" s="19"/>
+      <c r="I15" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="18"/>
     </row>
     <row r="16" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
@@ -1329,10 +1310,10 @@
       <c r="H16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I16" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J16" s="19"/>
+      <c r="I16" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="18"/>
     </row>
     <row r="17" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
@@ -1357,10 +1338,10 @@
       <c r="H17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J17" s="19"/>
+      <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
@@ -1385,10 +1366,10 @@
       <c r="H18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I18" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J18" s="19"/>
+      <c r="I18" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="18"/>
     </row>
     <row r="19" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
@@ -1413,10 +1394,10 @@
       <c r="H19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I19" s="18" t="s">
+      <c r="I19" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J19" s="19"/>
+      <c r="J19" s="18"/>
     </row>
     <row r="20" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
@@ -1441,10 +1422,10 @@
       <c r="H20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I20" s="18" t="s">
+      <c r="I20" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J20" s="19"/>
+      <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
@@ -1469,10 +1450,10 @@
       <c r="H21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I21" s="18" t="s">
+      <c r="I21" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J21" s="19"/>
+      <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
@@ -1497,10 +1478,10 @@
       <c r="H22" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="18" t="s">
+      <c r="I22" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J22" s="19"/>
+      <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
@@ -1527,10 +1508,10 @@
       <c r="H23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J23" s="19"/>
+      <c r="I23" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J23" s="18"/>
     </row>
     <row r="24" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
@@ -1555,10 +1536,10 @@
       <c r="H24" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J24" s="19"/>
+      <c r="I24" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J24" s="18"/>
     </row>
     <row r="25" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
@@ -1579,10 +1560,10 @@
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J25" s="19"/>
+      <c r="I25" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="18"/>
     </row>
     <row r="26" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
@@ -1607,10 +1588,10 @@
       <c r="H26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="J26" s="19"/>
+      <c r="I26" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" s="18"/>
     </row>
     <row r="27" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
@@ -1635,10 +1616,10 @@
       <c r="H27" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I27" s="18" t="s">
+      <c r="I27" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="19"/>
+      <c r="J27" s="18"/>
     </row>
     <row r="28" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
@@ -1663,10 +1644,10 @@
       <c r="H28" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I28" s="18" t="s">
+      <c r="I28" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J28" s="19"/>
+      <c r="J28" s="18"/>
     </row>
     <row r="29" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
@@ -1691,10 +1672,10 @@
       <c r="H29" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I29" s="18" t="s">
+      <c r="I29" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J29" s="19"/>
+      <c r="J29" s="18"/>
     </row>
     <row r="30" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
@@ -1719,10 +1700,10 @@
       <c r="H30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I30" s="18" t="s">
+      <c r="I30" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J30" s="19"/>
+      <c r="J30" s="18"/>
     </row>
     <row r="31" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
@@ -1747,10 +1728,10 @@
       <c r="H31" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I31" s="18" t="s">
+      <c r="I31" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="19"/>
+      <c r="J31" s="18"/>
     </row>
     <row r="32" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
@@ -1775,10 +1756,10 @@
       <c r="H32" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I32" s="18" t="s">
+      <c r="I32" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="J32" s="19"/>
+      <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
@@ -1803,10 +1784,10 @@
       <c r="H33" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I33" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="J33" s="23"/>
+      <c r="I33" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" s="20"/>
     </row>
     <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
@@ -1814,7 +1795,7 @@
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D34" s="7">
         <v>12246</v>
@@ -1826,15 +1807,15 @@
         <v>12904</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="I34" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="J34" s="17"/>
+        <v>85</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J34" s="16"/>
     </row>
     <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
@@ -1842,7 +1823,7 @@
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D35" s="7">
         <v>12246</v>
@@ -1854,77 +1835,21 @@
         <v>12904</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="I35" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="J35" s="17"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D36" s="7">
-        <v>12007</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" s="7">
-        <v>12905</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="I36" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="J36" s="17"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" s="7">
-        <v>12007</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="7">
-        <v>12905</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="I37" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="J37" s="17"/>
+      <c r="I35" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J37" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
+  <autoFilter ref="A1:J35" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
     <filterColumn colId="8" showButton="0"/>
   </autoFilter>
-  <mergeCells count="37">
+  <mergeCells count="35">
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="I19:J19"/>
@@ -1948,8 +1873,6 @@
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="I34:J34"/>
     <mergeCell ref="I35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="I33:J33"/>

--- a/data/Can Transitions 9_25.xlsx
+++ b/data/Can Transitions 9_25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/balapradeepkonda_alamancefoods_com/Documents/Documents/GitHub/Bala_Can_SupplyChain/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{B4A1369C-FDA8-4210-B800-9E801E204FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFBA1C11-1526-4839-B765-5E31B3801E0F}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{B4A1369C-FDA8-4210-B800-9E801E204FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E17D71AA-6C9D-4ECB-9C4E-9D1FCD82FE23}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
+    <workbookView xWindow="17064" yWindow="-14148" windowWidth="23040" windowHeight="12120" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$35</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="88">
   <si>
     <t>ITEM DESCRIPTION</t>
   </si>
@@ -300,6 +300,12 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>A36 </t>
+  </si>
+  <si>
+    <t>PK-A-CAN NON-DAIRY 15OZ CLASS</t>
   </si>
 </sst>
 </file>
@@ -373,7 +379,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -444,11 +450,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -490,29 +507,32 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -848,7 +868,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -886,10 +906,10 @@
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="22"/>
+      <c r="J1" s="18"/>
     </row>
     <row r="2" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -916,10 +936,10 @@
       <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="18"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -946,10 +966,10 @@
       <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="I3" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="18"/>
+      <c r="J3" s="16"/>
     </row>
     <row r="4" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
@@ -974,10 +994,10 @@
       <c r="H4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" s="18"/>
+      <c r="I4" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="16"/>
     </row>
     <row r="5" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
@@ -1002,10 +1022,10 @@
       <c r="H5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J5" s="18"/>
+      <c r="I5" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="16"/>
     </row>
     <row r="6" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
@@ -1030,10 +1050,10 @@
       <c r="H6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="18"/>
+      <c r="I6" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" s="16"/>
     </row>
     <row r="7" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
@@ -1058,10 +1078,10 @@
       <c r="H7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="18"/>
+      <c r="I7" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J7" s="16"/>
     </row>
     <row r="8" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
@@ -1086,10 +1106,10 @@
       <c r="H8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J8" s="18"/>
+      <c r="J8" s="16"/>
     </row>
     <row r="9" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
@@ -1114,10 +1134,10 @@
       <c r="H9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="18"/>
+      <c r="I9" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="16"/>
     </row>
     <row r="10" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
@@ -1142,10 +1162,10 @@
       <c r="H10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J10" s="18"/>
+      <c r="I10" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="16"/>
     </row>
     <row r="11" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
@@ -1170,10 +1190,10 @@
       <c r="H11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J11" s="18"/>
+      <c r="I11" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
@@ -1198,10 +1218,10 @@
       <c r="H12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J12" s="18"/>
+      <c r="I12" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -1226,10 +1246,10 @@
       <c r="H13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J13" s="18"/>
+      <c r="I13" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
@@ -1254,10 +1274,10 @@
       <c r="H14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" s="18"/>
+      <c r="I14" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
@@ -1282,10 +1302,10 @@
       <c r="H15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J15" s="18"/>
+      <c r="I15" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
@@ -1310,10 +1330,10 @@
       <c r="H16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I16" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J16" s="18"/>
+      <c r="I16" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="16"/>
     </row>
     <row r="17" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
@@ -1338,10 +1358,10 @@
       <c r="H17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J17" s="18"/>
+      <c r="J17" s="16"/>
     </row>
     <row r="18" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
@@ -1366,10 +1386,10 @@
       <c r="H18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I18" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J18" s="18"/>
+      <c r="I18" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="16"/>
     </row>
     <row r="19" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
@@ -1394,10 +1414,10 @@
       <c r="H19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I19" s="17" t="s">
+      <c r="I19" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J19" s="18"/>
+      <c r="J19" s="16"/>
     </row>
     <row r="20" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
@@ -1422,10 +1442,10 @@
       <c r="H20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I20" s="17" t="s">
+      <c r="I20" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J20" s="18"/>
+      <c r="J20" s="16"/>
     </row>
     <row r="21" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
@@ -1450,10 +1470,10 @@
       <c r="H21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I21" s="17" t="s">
+      <c r="I21" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J21" s="18"/>
+      <c r="J21" s="16"/>
     </row>
     <row r="22" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
@@ -1478,10 +1498,10 @@
       <c r="H22" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="17" t="s">
+      <c r="I22" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J22" s="18"/>
+      <c r="J22" s="16"/>
     </row>
     <row r="23" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
@@ -1508,10 +1528,10 @@
       <c r="H23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J23" s="18"/>
+      <c r="I23" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J23" s="16"/>
     </row>
     <row r="24" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
@@ -1536,10 +1556,10 @@
       <c r="H24" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J24" s="18"/>
+      <c r="I24" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J24" s="16"/>
     </row>
     <row r="25" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
@@ -1560,10 +1580,10 @@
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J25" s="18"/>
+      <c r="I25" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="16"/>
     </row>
     <row r="26" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
@@ -1588,10 +1608,10 @@
       <c r="H26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="J26" s="18"/>
+      <c r="I26" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" s="16"/>
     </row>
     <row r="27" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
@@ -1616,10 +1636,10 @@
       <c r="H27" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I27" s="17" t="s">
+      <c r="I27" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="18"/>
+      <c r="J27" s="16"/>
     </row>
     <row r="28" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
@@ -1644,10 +1664,10 @@
       <c r="H28" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I28" s="17" t="s">
+      <c r="I28" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J28" s="18"/>
+      <c r="J28" s="16"/>
     </row>
     <row r="29" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
@@ -1672,10 +1692,10 @@
       <c r="H29" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I29" s="17" t="s">
+      <c r="I29" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J29" s="18"/>
+      <c r="J29" s="16"/>
     </row>
     <row r="30" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
@@ -1700,10 +1720,10 @@
       <c r="H30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I30" s="17" t="s">
+      <c r="I30" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J30" s="18"/>
+      <c r="J30" s="16"/>
     </row>
     <row r="31" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
@@ -1728,10 +1748,10 @@
       <c r="H31" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I31" s="17" t="s">
+      <c r="I31" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="18"/>
+      <c r="J31" s="16"/>
     </row>
     <row r="32" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
@@ -1756,10 +1776,10 @@
       <c r="H32" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I32" s="17" t="s">
+      <c r="I32" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="J32" s="18"/>
+      <c r="J32" s="16"/>
     </row>
     <row r="33" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
@@ -1784,10 +1804,10 @@
       <c r="H33" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I33" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="J33" s="20"/>
+      <c r="I33" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" s="22"/>
     </row>
     <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
@@ -1812,10 +1832,10 @@
       <c r="H34" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="I34" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J34" s="16"/>
+      <c r="I34" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J34" s="20"/>
     </row>
     <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
@@ -1840,37 +1860,44 @@
       <c r="H35" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="I35" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J35" s="16"/>
+      <c r="I35" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" s="20"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="23">
+        <v>12337</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="23">
+        <v>12908</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="J36" s="20"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J35" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
     <filterColumn colId="8" showButton="0"/>
   </autoFilter>
-  <mergeCells count="35">
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
+  <mergeCells count="36">
+    <mergeCell ref="I36:J36"/>
     <mergeCell ref="I34:J34"/>
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="I16:J16"/>
@@ -1885,6 +1912,27 @@
     <mergeCell ref="I28:J28"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I22:J22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/data/Can Transitions 9_25.xlsx
+++ b/data/Can Transitions 9_25.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alamancefoods-my.sharepoint.com/personal/balapradeepkonda_alamancefoods_com/Documents/Documents/GitHub/Bala_Can_SupplyChain/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{B4A1369C-FDA8-4210-B800-9E801E204FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E17D71AA-6C9D-4ECB-9C4E-9D1FCD82FE23}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{B4A1369C-FDA8-4210-B800-9E801E204FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{889FFDD3-FA85-4CB0-B3B0-8EB74C80D493}"/>
   <bookViews>
-    <workbookView xWindow="17064" yWindow="-14148" windowWidth="23040" windowHeight="12120" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
+    <workbookView xWindow="11244" yWindow="-17472" windowWidth="30936" windowHeight="16776" xr2:uid="{691FB9E4-0905-4364-99F9-B696A478F86B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$34</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="88">
   <si>
     <t>ITEM DESCRIPTION</t>
   </si>
@@ -507,6 +507,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -529,9 +532,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -906,10 +906,10 @@
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="J1" s="18"/>
+      <c r="J1" s="19"/>
     </row>
     <row r="2" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -936,10 +936,10 @@
       <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="16"/>
+      <c r="J2" s="17"/>
     </row>
     <row r="3" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
@@ -966,10 +966,10 @@
       <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J3" s="16"/>
+      <c r="J3" s="17"/>
     </row>
     <row r="4" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
@@ -994,10 +994,10 @@
       <c r="H4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J4" s="16"/>
+      <c r="I4" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="17"/>
     </row>
     <row r="5" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
@@ -1022,10 +1022,10 @@
       <c r="H5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J5" s="16"/>
+      <c r="I5" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="17"/>
     </row>
     <row r="6" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
@@ -1050,10 +1050,10 @@
       <c r="H6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="16"/>
+      <c r="I6" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J6" s="17"/>
     </row>
     <row r="7" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
@@ -1078,10 +1078,10 @@
       <c r="H7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="16"/>
+      <c r="I7" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J7" s="17"/>
     </row>
     <row r="8" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
@@ -1106,10 +1106,10 @@
       <c r="H8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J8" s="16"/>
+      <c r="J8" s="17"/>
     </row>
     <row r="9" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
@@ -1134,10 +1134,10 @@
       <c r="H9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="16"/>
+      <c r="I9" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="17"/>
     </row>
     <row r="10" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
@@ -1162,10 +1162,10 @@
       <c r="H10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J10" s="16"/>
+      <c r="I10" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
@@ -1190,10 +1190,10 @@
       <c r="H11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J11" s="16"/>
+      <c r="I11" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J11" s="17"/>
     </row>
     <row r="12" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
@@ -1218,10 +1218,10 @@
       <c r="H12" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J12" s="16"/>
+      <c r="I12" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="17"/>
     </row>
     <row r="13" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
@@ -1246,10 +1246,10 @@
       <c r="H13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J13" s="16"/>
+      <c r="I13" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="17"/>
     </row>
     <row r="14" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
@@ -1274,10 +1274,10 @@
       <c r="H14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" s="16"/>
+      <c r="I14" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
@@ -1302,10 +1302,10 @@
       <c r="H15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J15" s="16"/>
+      <c r="I15" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J15" s="17"/>
     </row>
     <row r="16" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
@@ -1330,10 +1330,10 @@
       <c r="H16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I16" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J16" s="16"/>
+      <c r="I16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="17"/>
     </row>
     <row r="17" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
@@ -1358,10 +1358,10 @@
       <c r="H17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J17" s="16"/>
+      <c r="J17" s="17"/>
     </row>
     <row r="18" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
@@ -1386,10 +1386,10 @@
       <c r="H18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I18" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J18" s="16"/>
+      <c r="I18" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="17"/>
     </row>
     <row r="19" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
@@ -1414,10 +1414,10 @@
       <c r="H19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J19" s="16"/>
+      <c r="J19" s="17"/>
     </row>
     <row r="20" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
@@ -1442,10 +1442,10 @@
       <c r="H20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="I20" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J20" s="16"/>
+      <c r="J20" s="17"/>
     </row>
     <row r="21" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
@@ -1470,10 +1470,10 @@
       <c r="H21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I21" s="15" t="s">
+      <c r="I21" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J21" s="16"/>
+      <c r="J21" s="17"/>
     </row>
     <row r="22" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
@@ -1498,10 +1498,10 @@
       <c r="H22" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I22" s="15" t="s">
+      <c r="I22" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J22" s="16"/>
+      <c r="J22" s="17"/>
     </row>
     <row r="23" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
@@ -1528,10 +1528,10 @@
       <c r="H23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J23" s="16"/>
+      <c r="I23" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J23" s="17"/>
     </row>
     <row r="24" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
@@ -1556,10 +1556,10 @@
       <c r="H24" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J24" s="16"/>
+      <c r="I24" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J24" s="17"/>
     </row>
     <row r="25" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
@@ -1578,12 +1578,16 @@
       <c r="F25" s="7">
         <v>12893</v>
       </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J25" s="16"/>
+      <c r="G25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="17"/>
     </row>
     <row r="26" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
@@ -1608,10 +1612,10 @@
       <c r="H26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="J26" s="16"/>
+      <c r="I26" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" s="17"/>
     </row>
     <row r="27" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
@@ -1636,10 +1640,10 @@
       <c r="H27" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="I27" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="16"/>
+      <c r="J27" s="17"/>
     </row>
     <row r="28" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
@@ -1664,10 +1668,10 @@
       <c r="H28" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="I28" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J28" s="16"/>
+      <c r="J28" s="17"/>
     </row>
     <row r="29" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
@@ -1686,16 +1690,16 @@
       <c r="F29" s="7">
         <v>12869</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I29" s="15" t="s">
+      <c r="G29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J29" s="16"/>
+      <c r="J29" s="17"/>
     </row>
     <row r="30" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
@@ -1720,27 +1724,27 @@
       <c r="H30" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="I30" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J30" s="16"/>
+      <c r="J30" s="17"/>
     </row>
     <row r="31" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D31" s="7">
-        <v>12401</v>
+        <v>12036</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F31" s="7">
-        <v>12867</v>
+        <v>12868</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>9</v>
@@ -1748,70 +1752,70 @@
       <c r="H31" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="I31" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="16"/>
+      <c r="J31" s="17"/>
     </row>
     <row r="32" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D32" s="7">
-        <v>12036</v>
+        <v>12278</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F32" s="7">
-        <v>12868</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>9</v>
+        <v>12410</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I32" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="J32" s="16"/>
-    </row>
-    <row r="33" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="8" t="s">
-        <v>68</v>
+      <c r="I32" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="J32" s="23"/>
+    </row>
+    <row r="33" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="D33" s="7">
-        <v>12278</v>
+        <v>12246</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>7</v>
       </c>
       <c r="F33" s="7">
-        <v>12410</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="I33" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="J33" s="22"/>
+        <v>12904</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="J33" s="21"/>
     </row>
     <row r="34" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="13" t="s">
@@ -1832,54 +1836,54 @@
       <c r="H34" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="I34" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="J34" s="20"/>
-    </row>
-    <row r="35" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D35" s="7">
-        <v>12246</v>
+      <c r="I34" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="J34" s="21"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="15">
+        <v>12337</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F35" s="7">
-        <v>12904</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>85</v>
+      <c r="F35" s="15">
+        <v>12908</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="H35" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="I35" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="J35" s="20"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" s="23">
-        <v>12337</v>
+      <c r="I35" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" s="21"/>
+    </row>
+    <row r="36" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B36" s="7"/>
+      <c r="C36" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="7">
+        <v>12867</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F36" s="23">
-        <v>12908</v>
+      <c r="F36" s="7">
+        <v>12902</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>8</v>
@@ -1887,22 +1891,19 @@
       <c r="H36" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="I36" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="J36" s="20"/>
+      <c r="I36" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="J36" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J35" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
+  <autoFilter ref="A1:J34" xr:uid="{F3192465-F364-4878-96B2-165F606027ED}">
     <filterColumn colId="8" showButton="0"/>
   </autoFilter>
   <mergeCells count="36">
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="I35:J35"/>
     <mergeCell ref="I16:J16"/>
+    <mergeCell ref="I31:J31"/>
     <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I33:J33"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="I25:J25"/>
@@ -1927,12 +1928,15 @@
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="I36:J36"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I34:J34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
